--- a/artfynd/A 45941-2025 artfynd.xlsx
+++ b/artfynd/A 45941-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55128317</v>
+        <v>16626250</v>
       </c>
       <c r="B2" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,16 +703,8 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -725,13 +712,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329221.0894316813</v>
+        <v>329217</v>
       </c>
       <c r="R2" t="n">
-        <v>6455761.820150483</v>
+        <v>6455711</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,15 +756,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrmatta i rik granskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -800,6 +771,119 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>55128317</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Valdalsbergens NR, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>329221</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6455762</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-09-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-09-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>barrmatta i rik granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45941-2025 artfynd.xlsx
+++ b/artfynd/A 45941-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16626250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55128317</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>